--- a/ScriptVB/modelo_instrutores.xlsx
+++ b/ScriptVB/modelo_instrutores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://enginetecnologia-my.sharepoint.com/personal/ffasti_enginetecnologia_com_br/Documents/Projetos/Claude/Projetos/AlocacaoInstrutores/ScriptVB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{EBD2D2FF-38BF-4474-9999-3ED59685501A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACE8DC40-BFBB-4031-92FA-568817D51A29}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2BF809F3-B938-42BC-87F7-340A208E9101}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1260" yWindow="36" windowWidth="20940" windowHeight="11868" xr2:uid="{7D88D84A-9087-45D0-9581-64987B9B4F79}"/>
+    <workbookView xWindow="1260" yWindow="36" windowWidth="20940" windowHeight="11868" xr2:uid="{651A5279-8AEC-4FAA-9077-4B2B57E5FDFA}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrutores" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="40">
   <si>
     <t>nome</t>
   </si>
@@ -50,9 +50,6 @@
     <t>turnos</t>
   </si>
   <si>
-    <t>carga_horaria_turno</t>
-  </si>
-  <si>
     <t>dias_semana</t>
   </si>
   <si>
@@ -68,10 +65,7 @@
     <t>Jovem Digital</t>
   </si>
   <si>
-    <t>manha;tarde</t>
-  </si>
-  <si>
-    <t>4;4</t>
+    <t>manha_1;manha_2;tarde_1</t>
   </si>
   <si>
     <t>2;3;4;5</t>
@@ -89,9 +83,6 @@
     <t>noite</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>2;4</t>
   </si>
   <si>
@@ -107,10 +98,7 @@
     <t>Inclusão Tech</t>
   </si>
   <si>
-    <t>manha;noite</t>
-  </si>
-  <si>
-    <t>4;3</t>
+    <t>manha_1;noite</t>
   </si>
   <si>
     <t>2;3;4;5;6</t>
@@ -122,10 +110,7 @@
     <t>Carlos Pereira</t>
   </si>
   <si>
-    <t>tarde</t>
-  </si>
-  <si>
-    <t>4</t>
+    <t>tarde_1</t>
   </si>
   <si>
     <t>3;5</t>
@@ -137,7 +122,7 @@
     <t>Beatriz Lima</t>
   </si>
   <si>
-    <t>manha</t>
+    <t>manha_1;manha_2</t>
   </si>
   <si>
     <t>2;3;4</t>
@@ -152,16 +137,16 @@
     <t>Conecta Jovem</t>
   </si>
   <si>
-    <t>tarde;noite</t>
-  </si>
-  <si>
-    <t>3;3</t>
+    <t>tarde_1;noite</t>
   </si>
   <si>
     <t>Robótica;Pixel Art</t>
   </si>
   <si>
     <t>Juliana Alves</t>
+  </si>
+  <si>
+    <t>manha_1;tarde_1;tarde_2</t>
   </si>
   <si>
     <t>2;4;5</t>
@@ -217,25 +202,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -569,30 +539,29 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB1D384E-E75B-4052-AC24-586E7CFE18BD}">
-  <dimension ref="A1:G9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D0416D9-563C-41A1-BEAF-D59BC6863A70}">
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.33203125" customWidth="1"/>
+    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.88671875" style="5" customWidth="1"/>
-    <col min="4" max="4" width="17.5546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="29.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -601,192 +570,165 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="E2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="E3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="F3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="2" t="s">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="F4" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="B5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="B6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="B7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="4" t="s">
+      <c r="C7" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="D7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="B8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="E8" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="F8" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="2" t="s">
+      <c r="B9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>44</v>
       </c>
     </row>
   </sheetData>
